--- a/AAII_Financials/Yearly/CRNCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRNCY_YR_FIN.xlsx
@@ -894,10 +894,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>10300</v>
+        <v>-300</v>
       </c>
       <c r="E14" s="3">
-        <v>-15600</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
         <v>46900</v>
@@ -927,10 +927,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>50800</v>
+        <v>61400</v>
       </c>
       <c r="E15" s="3">
-        <v>85100</v>
+        <v>69400</v>
       </c>
       <c r="F15" s="3">
         <v>120400</v>
@@ -972,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>119500</v>
+        <v>130100</v>
       </c>
       <c r="E17" s="3">
-        <v>163500</v>
+        <v>147800</v>
       </c>
       <c r="F17" s="3">
         <v>298800</v>
@@ -1005,10 +1005,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15400</v>
+        <v>4800</v>
       </c>
       <c r="E18" s="3">
-        <v>-15700</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>-97800</v>
